--- a/128-ig-compléter-la-page-sécurité-dans-longlet-autres-ressources/ig/all-profiles.xlsx
+++ b/128-ig-compléter-la-page-sécurité-dans-longlet-autres-ressources/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-25T12:12:13+00:00</t>
+    <t>2024-09-25T13:27:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/128-ig-compléter-la-page-sécurité-dans-longlet-autres-ressources/ig/all-profiles.xlsx
+++ b/128-ig-compléter-la-page-sécurité-dans-longlet-autres-ressources/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-25T13:27:10+00:00</t>
+    <t>2024-09-25T13:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/128-ig-compléter-la-page-sécurité-dans-longlet-autres-ressources/ig/all-profiles.xlsx
+++ b/128-ig-compléter-la-page-sécurité-dans-longlet-autres-ressources/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-25T13:28:56+00:00</t>
+    <t>2024-09-25T13:52:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/128-ig-compléter-la-page-sécurité-dans-longlet-autres-ressources/ig/all-profiles.xlsx
+++ b/128-ig-compléter-la-page-sécurité-dans-longlet-autres-ressources/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-25T13:52:55+00:00</t>
+    <t>2024-09-25T13:59:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
